--- a/excel_files/工程檔目錄_2026.xlsx
+++ b/excel_files/工程檔目錄_2026.xlsx
@@ -1,31 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHIEN\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94ABF200-F436-4C6E-91C7-04C4E80B3442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBEEE954-FBAB-432B-868A-D33EA69439C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7BC8074A-6CC3-4D72-BD80-F3040C41499B}"/>
+    <workbookView xWindow="3345" yWindow="1275" windowWidth="25455" windowHeight="14925" xr2:uid="{4EE896CC-7187-4CEE-8BC8-6368AED9982C}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>工程案號</t>
   </si>
@@ -129,12 +138,6 @@
     <t>WT_地震搶修_F12P3_DI Tank震後破損維修工程_桶槽修繕及6S</t>
   </si>
   <si>
-    <t>W26-021</t>
-  </si>
-  <si>
-    <t>半導體參展模組</t>
-  </si>
-  <si>
     <t>W26-022</t>
   </si>
   <si>
@@ -147,12 +150,6 @@
     <t>Y2026_LDS養蝦循環水系統-基礎設施 (原W24-002轉)</t>
   </si>
   <si>
-    <t>W26-024</t>
-  </si>
-  <si>
-    <t>林莊淨水廠VPN及PLC維修&amp;加藥偵測管路檢修</t>
-  </si>
-  <si>
     <t>W26-025</t>
   </si>
   <si>
@@ -165,12 +162,6 @@
     <t xml:space="preserve">63TF051_F3 NHF sensor自清系統建置  </t>
   </si>
   <si>
-    <t>W26-028</t>
-  </si>
-  <si>
-    <t>台東_自來水公司_底泥採樣量測設備(第十區)</t>
-  </si>
-  <si>
     <t>W26-029</t>
   </si>
   <si>
@@ -207,12 +198,6 @@
     <t>Y2026_F12P1_機電_Office B4 汙水坑緊急修繕工程</t>
   </si>
   <si>
-    <t>W26-036</t>
-  </si>
-  <si>
-    <t>代買電動驅動器(Q24-035自動洗車台建置案)</t>
-  </si>
-  <si>
     <t>W26-037</t>
   </si>
   <si>
@@ -237,6 +222,12 @@
     <t>臨時管路改善</t>
   </si>
   <si>
+    <t>W26-041</t>
+  </si>
+  <si>
+    <t>地下水井沉水泵更換</t>
+  </si>
+  <si>
     <t>W26-066</t>
   </si>
   <si>
@@ -333,12 +324,6 @@
     <t>Y2025_F12P1_機電_B4F生活汙廢水泵浦更換及修繕工程</t>
   </si>
   <si>
-    <t>W25-015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">緊急搶修_WT_工程_ F12P45 生活汙水沉水泵更換工程 </t>
-  </si>
-  <si>
     <t>W25-022</t>
   </si>
   <si>
@@ -393,22 +378,10 @@
     <t xml:space="preserve">AP3-BP-CoW-2H24_SP1_排水管路及加藥管路工程 </t>
   </si>
   <si>
-    <t>W24-070</t>
-  </si>
-  <si>
-    <t>WT_穩定運轉_P45 ICW 及 CW 進水氣動閥組維修及備品購買</t>
-  </si>
-  <si>
     <t>W23-030</t>
   </si>
   <si>
     <t>給排水_office冷凝排水主管增設維修口緊急搶修工程</t>
-  </si>
-  <si>
-    <t>W22-036</t>
-  </si>
-  <si>
-    <t>Y2022_F12P7_給排水_生活汙水管路檢修</t>
   </si>
 </sst>
 </file>
@@ -771,8 +744,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189A468B-EA7E-4903-BEC4-DE81B9283C85}">
-  <dimension ref="A1:B64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1BC22C-E7EE-40A0-94A7-35E29F3031FA}">
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -1243,54 +1216,6 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" t="s">
-        <v>127</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/工程檔目錄_2026.xlsx
+++ b/excel_files/工程檔目錄_2026.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHIEN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBEEE954-FBAB-432B-868A-D33EA69439C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E314918B-2E3D-40AF-8F8F-91306289DB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3345" yWindow="1275" windowWidth="25455" windowHeight="14925" xr2:uid="{4EE896CC-7187-4CEE-8BC8-6368AED9982C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4EE896CC-7187-4CEE-8BC8-6368AED9982C}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -427,9 +418,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -745,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1BC22C-E7EE-40A0-94A7-35E29F3031FA}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -753,470 +747,478 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>114</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
